--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98492</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573812.5399609673</v>
+        <v>573813</v>
       </c>
       <c r="R2" t="n">
-        <v>6447700.441310958</v>
+        <v>6447700</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>101323</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573812.5399609673</v>
+        <v>573813</v>
       </c>
       <c r="R3" t="n">
-        <v>6447700.441310958</v>
+        <v>6447700</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -930,12 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573812.5399609673</v>
+        <v>573813</v>
       </c>
       <c r="R4" t="n">
-        <v>6447700.441310958</v>
+        <v>6447700</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1000,19 +965,9 @@
           <t>1982-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103672</v>
+        <v>103680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103680</v>
+        <v>103682</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103682</v>
+        <v>103709</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103709</v>
+        <v>103715</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103715</v>
+        <v>103722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103722</v>
+        <v>103726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103726</v>
+        <v>103733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103736</v>
+        <v>103741</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103741</v>
+        <v>103749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74128596</v>
       </c>
       <c r="B2" t="n">
-        <v>98563</v>
+        <v>98573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74116483</v>
       </c>
       <c r="B3" t="n">
-        <v>103749</v>
+        <v>103759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>74860836</v>
       </c>
       <c r="B4" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74128596</v>
+        <v>72576133</v>
       </c>
       <c r="B2" t="n">
-        <v>98573</v>
+        <v>91920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220093</v>
+        <v>1205</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>10 Långgöl SV hörnet, Sm</t>
+          <t>Långsjön, Åsens NR, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573813</v>
+        <v>574046</v>
       </c>
       <c r="R2" t="n">
-        <v>6447700</v>
+        <v>6447865</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +750,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2018-06-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
+          <t>2018-06-19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Corallorhiza trifida. LEG: Erik Moberger</t>
+          <t>På stor asp vid vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,37 +769,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsmark-alkärr</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74116483</v>
+        <v>102351825</v>
       </c>
       <c r="B3" t="n">
-        <v>103759</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +799,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222395</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långgöl, SV-hörnet, Sm</t>
+          <t>Långgöl nord, Hannäs kyrka, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573813</v>
+        <v>574049</v>
       </c>
       <c r="R3" t="n">
-        <v>6447700</v>
+        <v>6447876</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1982-12-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Circaea alpina. LEG: Erik Moberger</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -870,37 +878,49 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Alkärr</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74860836</v>
+        <v>95043141</v>
       </c>
       <c r="B4" t="n">
-        <v>105732</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,37 +928,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100045</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>10 Långgöl SV hörnet, Sm</t>
+          <t>Långgöl, Falerum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573813</v>
+        <v>574061</v>
       </c>
       <c r="R4" t="n">
-        <v>6447700</v>
+        <v>6447833</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,17 +998,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1982-01-01</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1984-12-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Pyrola chlorantha. LEG: Erik Moberger</t>
+          <t>2021-07-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,44 +1024,30 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Skogsmark-alkärr</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Mari Sandell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Mari Sandell</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>95043143</v>
       </c>
       <c r="B5" t="n">
-        <v>55511</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1060,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574061.1820588349</v>
+        <v>574061</v>
       </c>
       <c r="R5" t="n">
-        <v>6447833.301545857</v>
+        <v>6447833</v>
       </c>
       <c r="S5" t="n">
         <v>17</v>
@@ -1129,6 +1156,1511 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>78626039</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>573833</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6447760</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stilla bredvid väg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>78626040</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>573820</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6447747</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stilla bredvid väg</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>78626041</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573814</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6447696</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>78626046</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>574133</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6447882</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>78626049</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>573999</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6447816</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>78626042</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>573814</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6447696</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>78626043</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>573862</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6447751</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>78626045</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>574166</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6447948</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>78626047</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>574143</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6447903</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>78626048</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>38, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>573987</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6447814</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2019-04-24</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spelande</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74128596</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>10 Långgöl SV hörnet, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>573813</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6447700</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>1984-12-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Corallorhiza trifida. LEG: Erik Moberger</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Skogsmark-alkärr</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74860836</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>10 Långgöl SV hörnet, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>573813</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6447700</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>1984-12-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Pyrola chlorantha. LEG: Erik Moberger</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Skogsmark-alkärr</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>74116483</v>
+      </c>
+      <c r="B18" t="n">
+        <v>104252</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långgöl, SV-hörnet, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>573813</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6447700</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Åtvidaberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hannäs</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1982-01-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1982-12-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 7G9f 4014. SOM: Circaea alpina. LEG: Erik Moberger</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Alkärr</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21664-2025 artfynd.xlsx
+++ b/artfynd/A 21664-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72576133</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102351825</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95043141</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1156,6 +1176,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95043143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1272,6 +1297,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626039</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626040</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1504,6 +1539,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626041</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1626,6 +1666,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626046</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1742,6 +1787,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626049</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1858,6 +1908,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626042</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1974,6 +2029,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626043</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2090,6 +2150,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626045</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2212,6 +2277,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626047</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2328,6 +2398,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78626048</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2439,6 +2514,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74128596</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2550,6 +2630,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74860836</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2661,8 +2746,32 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74116483</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>